--- a/sample_requests.xlsx
+++ b/sample_requests.xlsx
@@ -1,40 +1,446 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28200" windowHeight="12990"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="20">
+  <si>
+    <t>activity_list</t>
+  </si>
+  <si>
+    <t>dataset_path</t>
+  </si>
+  <si>
+    <t>camera_url</t>
+  </si>
+  <si>
+    <t>camera_user</t>
+  </si>
+  <si>
+    <t>camera_pass</t>
+  </si>
+  <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>subtype</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>starttime</t>
+  </si>
+  <si>
+    <t>clip_duration</t>
+  </si>
+  <si>
+    <t>skip_duration</t>
+  </si>
+  <si>
+    <t>total_duration</t>
+  </si>
+  <si>
+    <t>label_delay</t>
+  </si>
+  <si>
+    <t>using_computer, using_phone</t>
+  </si>
+  <si>
+    <t>/home/hexylon/Documents/meet/activity_detection/test_Activity_detection_dataset</t>
+  </si>
+  <si>
+    <t>111.93.234.134:532</t>
+  </si>
+  <si>
+    <t>stream</t>
+  </si>
+  <si>
+    <t>Stream@1234</t>
+  </si>
+  <si>
+    <t>playback</t>
+  </si>
+  <si>
+    <t>2026_06_22_09_30_00</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -42,85 +448,330 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,197 +1054,442 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="33.4" customWidth="1"/>
+    <col min="2" max="2" width="22.5" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="11.1" customWidth="1"/>
+    <col min="5" max="5" width="12.6" customWidth="1"/>
+    <col min="6" max="6" width="7.3" customWidth="1"/>
+    <col min="7" max="7" width="7.5" customWidth="1"/>
+    <col min="8" max="8" width="8.1" customWidth="1"/>
+    <col min="9" max="9" width="20.2" customWidth="1"/>
+    <col min="10" max="10" width="11.2" customWidth="1"/>
+    <col min="11" max="11" width="11.8" customWidth="1"/>
+    <col min="12" max="12" width="12.1" customWidth="1"/>
+    <col min="13" max="13" width="9.8" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>activity_list</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>dataset_path</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>camera_url</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>camera_user</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>camera_pass</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>channel</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>subtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>starttime</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>clip_duration</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>skip_duration</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>total_duration</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>label_delay</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>using_computer,working_with_machine</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>dataset_downloaded/test1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>137.97.199.242:510</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Stream@1234</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1">
+        <v>69</v>
+      </c>
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>playback</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026_06_22_12_00_00</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2">
         <v>4</v>
       </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
+      <c r="K2">
+        <v>50</v>
+      </c>
+      <c r="L2">
+        <v>3600</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>using_phone</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dataset_downloaded/test2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>137.97.199.242:510</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>stream</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stream@1234</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>35</v>
-      </c>
-      <c r="G3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1">
+        <v>70</v>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>playback</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026_06_22_12_45_00</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
+        <v>50</v>
+      </c>
+      <c r="L3">
+        <v>3600</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1">
+        <v>71</v>
+      </c>
+      <c r="G4">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4">
+        <v>3600</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
+        <v>72</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>50</v>
+      </c>
+      <c r="L5">
+        <v>3600</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="13.5" spans="1:13">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6">
+        <v>3600</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" spans="1:13">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>50</v>
+      </c>
+      <c r="L7">
+        <v>3600</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="13.5" spans="1:13">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8">
+        <v>3600</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="13.5" spans="1:13">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1">
+        <v>76</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>50</v>
+      </c>
+      <c r="L9">
+        <v>3600</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" ht="13.5" spans="1:13">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>50</v>
+      </c>
+      <c r="L10">
+        <v>3600</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/sample_requests.xlsx
+++ b/sample_requests.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="20">
   <si>
     <t>activity_list</t>
   </si>
@@ -82,10 +82,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -102,8 +102,85 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -111,7 +188,43 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -132,119 +245,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -255,61 +255,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,60 +423,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -387,55 +435,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,20 +464,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -497,28 +494,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -561,151 +550,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1060,7 +1060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="33.4" customWidth="1"/>
@@ -1119,7 +1119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" ht="13.5" spans="1:13">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>4</v>
       </c>
       <c r="K2">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L2">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" ht="13.5" spans="1:13">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>17</v>
       </c>
       <c r="F3" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1192,10 +1192,10 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L3">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -1218,7 +1218,7 @@
         <v>17</v>
       </c>
       <c r="F4" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1233,10 +1233,10 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L4">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -1259,7 +1259,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1274,10 +1274,10 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L5">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -1300,7 +1300,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1315,10 +1315,10 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L6">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -1341,7 +1341,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1356,10 +1356,10 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L7">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M7">
         <v>3</v>
@@ -1382,7 +1382,7 @@
         <v>17</v>
       </c>
       <c r="F8" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L8">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -1423,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="F9" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1438,53 +1438,12 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="L9">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="M9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="13.5" spans="1:13">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="1">
-        <v>77</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-      <c r="K10">
-        <v>50</v>
-      </c>
-      <c r="L10">
-        <v>3600</v>
-      </c>
-      <c r="M10">
         <v>3</v>
       </c>
     </row>
